--- a/Result/profitability/5483.xlsx
+++ b/Result/profitability/5483.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.94</v>
       </c>
       <c r="M2" t="n">
-        <v>1.705</v>
+        <v>1.81</v>
       </c>
       <c r="N2" t="n">
-        <v>26.4125</v>
+        <v>25.65</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.64</v>
       </c>
       <c r="M3" t="n">
-        <v>1.74125</v>
+        <v>2.0375</v>
       </c>
       <c r="N3" t="n">
-        <v>26.11625</v>
+        <v>25.23125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.94875</v>
+        <v>2.19875</v>
       </c>
       <c r="N4" t="n">
-        <v>25.93125</v>
+        <v>25.48875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>1.94875</v>
+        <v>2.20125</v>
       </c>
       <c r="N5" t="n">
-        <v>24.08375</v>
+        <v>23.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.855</v>
+        <v>2.04</v>
       </c>
       <c r="N6" t="n">
-        <v>22.115</v>
+        <v>22.42</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>1.66125</v>
+        <v>1.73125</v>
       </c>
       <c r="N7" t="n">
-        <v>20.64</v>
+        <v>19.93125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3575</v>
+        <v>1.5275</v>
       </c>
       <c r="N8" t="n">
-        <v>18.0175</v>
+        <v>17.94375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>21119</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16335</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4784</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2248</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3216</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5464</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1959</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.86125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.55125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7431693989071038</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0253872633390706</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.726495726495727</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.670000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1054502369668248</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
